--- a/library/relay.xlsx
+++ b/library/relay.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D1387CC-A9B4-409B-88D4-B837EE3135EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96E7164C-AD14-4262-BD3E-276EFE2B1C40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="19">
   <si>
     <t>Part Number</t>
   </si>
@@ -641,6 +641,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.85546875" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" customWidth="1"/>
     <col min="3" max="3" width="18.28515625" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
     <col min="5" max="5" width="14.7109375" customWidth="1"/>
@@ -683,13 +684,16 @@
       <c r="C2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>11</v>
+      <c r="D2" t="s">
+        <v>10</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>12</v>
       </c>
     </row>
@@ -703,13 +707,16 @@
       <c r="C3" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>11</v>
+      <c r="D3" t="s">
+        <v>14</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" t="s">
         <v>8</v>
       </c>
     </row>
@@ -717,7 +724,7 @@
       <c r="A4" t="s">
         <v>15</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>15</v>
       </c>
     </row>
@@ -727,16 +734,16 @@
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
-      <c r="E5" s="4" t="s">
+      <c r="F5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>17</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>17</v>
       </c>
     </row>
@@ -744,7 +751,7 @@
       <c r="A7" t="s">
         <v>18</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>18</v>
       </c>
     </row>

--- a/library/relay.xlsx
+++ b/library/relay.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96E7164C-AD14-4262-BD3E-276EFE2B1C40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E5C484A-8DA1-4A55-A3A2-57BA26F1A1D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="20">
   <si>
     <t>Part Number</t>
   </si>
@@ -91,6 +91,9 @@
   </si>
   <si>
     <t>Relay_4</t>
+  </si>
+  <si>
+    <t>Relay_5</t>
   </si>
 </sst>
 </file>
@@ -710,8 +713,8 @@
       <c r="D3" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>11</v>
+      <c r="E3" t="s">
+        <v>19</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>11</v>

--- a/library/relay.xlsx
+++ b/library/relay.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E5C484A-8DA1-4A55-A3A2-57BA26F1A1D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09DA49E2-5EA4-461F-ADFE-DA815AAE4957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="relay" sheetId="5" r:id="rId1"/>
@@ -29,12 +29,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="22">
   <si>
     <t>Part Number</t>
   </si>
@@ -94,6 +97,12 @@
   </si>
   <si>
     <t>Relay_5</t>
+  </si>
+  <si>
+    <t>HFD4/5SR (IM03GR)</t>
+  </si>
+  <si>
+    <t>HFD4/5SR</t>
   </si>
 </sst>
 </file>
@@ -344,9 +353,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office 2013–2022">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -384,7 +393,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -490,7 +499,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -632,7 +641,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -640,7 +649,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99D7E81C-1413-426F-8EBE-717C09928723}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.85546875" customWidth="1"/>
@@ -725,36 +734,59 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" t="s">
-        <v>15</v>
+        <v>20</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="F5" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="4"/>
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" t="s">
-        <v>17</v>
-      </c>
+      <c r="A6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="F6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="4"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>18</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F8" t="s">
         <v>18</v>
       </c>
     </row>

--- a/library/relay.xlsx
+++ b/library/relay.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10112"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\elem_altium_db2\library\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/garou/Documents/work/elem_altium_db2/library/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09DA49E2-5EA4-461F-ADFE-DA815AAE4957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CAFEC48-ECCE-0A48-9C14-C409B8AEA4F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29040" windowHeight="15720" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="relay" sheetId="5" r:id="rId1"/>
@@ -317,6 +317,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="21">
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный 2" xfId="2" xr:uid="{5A4A247A-9E13-45F7-8C42-156984DFCA88}"/>
     <cellStyle name="Accent 1 1" xfId="3" xr:uid="{59C07D72-8E19-46CF-887A-3117F6F3785F}"/>
     <cellStyle name="Accent 2 1" xfId="4" xr:uid="{6BABBE6D-B89F-40A5-B377-65A1ECF4F8D6}"/>
     <cellStyle name="Accent 3 1" xfId="5" xr:uid="{4C06F33B-F628-495C-9BA2-60FAC1B8690A}"/>
@@ -336,8 +338,6 @@
     <cellStyle name="Status 1" xfId="17" xr:uid="{B5CEB193-82F1-4869-9033-6CA5CF994AD1}"/>
     <cellStyle name="Text 1" xfId="18" xr:uid="{82FD0F21-4428-49B3-91A7-88A1E12D7A17}"/>
     <cellStyle name="Warning 1" xfId="19" xr:uid="{C0F92B33-BA6B-43EB-9AF1-3DB4037EF412}"/>
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 2" xfId="2" xr:uid="{5A4A247A-9E13-45F7-8C42-156984DFCA88}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -650,17 +650,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99D7E81C-1413-426F-8EBE-717C09928723}">
   <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.85546875" customWidth="1"/>
-    <col min="2" max="2" width="12.85546875" customWidth="1"/>
-    <col min="3" max="3" width="18.28515625" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" customWidth="1"/>
-    <col min="6" max="7" width="16.5703125" customWidth="1"/>
+    <col min="1" max="2" width="20.83203125" customWidth="1"/>
+    <col min="3" max="3" width="25.83203125" customWidth="1"/>
+    <col min="4" max="8" width="20.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -686,7 +683,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -709,7 +706,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -732,7 +729,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -755,7 +752,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -763,7 +760,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>16</v>
       </c>
@@ -774,7 +771,7 @@
       </c>
       <c r="G6" s="4"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -782,7 +779,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>18</v>
       </c>
